--- a/Day_02_Data_cleaning.xlsx
+++ b/Day_02_Data_cleaning.xlsx
@@ -1,29 +1,343 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f5c7b832c0e5f38/Documents/My projects/100-days-of-data-repository/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_F25DC773A252ABDACC1048A7095F46125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A74BD50-466E-4CFD-A4DE-DBFFE6D32662}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="8700" yWindow="380" windowWidth="10570" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="95">
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Transaction Date</t>
+  </si>
+  <si>
+    <t>Value Date</t>
+  </si>
+  <si>
+    <t>Posted Date</t>
+  </si>
+  <si>
+    <t>Pay In</t>
+  </si>
+  <si>
+    <t>PAY OUT</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>2/28/2026</t>
+  </si>
+  <si>
+    <t>2/28/2026 7:03:36 AM</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 25FEB 26</t>
+  </si>
+  <si>
+    <t>2/28/2026 9:52:19 AM</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 26FEB 26</t>
+  </si>
+  <si>
+    <t>2/28/2026 2:13:50 PM</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 27FEB 26</t>
+  </si>
+  <si>
+    <t>COB TRANSFER FROM AAA FINANC **4574 -</t>
+  </si>
+  <si>
+    <t>ipNXNi_t5896611628i4230interswitchdeLANG</t>
+  </si>
+  <si>
+    <t>ATM</t>
+  </si>
+  <si>
+    <t>ATM TRANSFER @10570663-Plot 43, Kofo Abayomi Stre</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-INTERBANK-S43604936-03-03-2026</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-WEB-S43285711-03-03-2026</t>
+  </si>
+  <si>
+    <t>ATM TRANSFER @10570662-ZIB Kofo Abayomi Br</t>
+  </si>
+  <si>
+    <t>ATM TRANSFER @12322576-PLOT 300 ADEOLA ODEKU  STR</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-INTERBANK-S48916203-05-03-2026</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-INTERBANK-S49299664-05-03-2026</t>
+  </si>
+  <si>
+    <t>Point of Sale</t>
+  </si>
+  <si>
+    <t>POS PURCHASE @205778PY-PIKWIK NIGERIA LIMITED PL</t>
+  </si>
+  <si>
+    <t>POS PURCHASE @2ISW313B-SPAR  ADEOLA ODEKU GURULA</t>
+  </si>
+  <si>
+    <t>ATM WITHDRAWAL @10702291-102 APAPA ROAD         E</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-POS-S57646840-09-03-2026</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 02MAR 26</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 03MAR 26</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 05MAR 26</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 06MAR 26</t>
+  </si>
+  <si>
+    <t>POS PURCHASE @2057RW2N-11 PLC                 1</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 09MAR 26</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-POS-S68880237-11-03-2026</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 11MAR 26</t>
+  </si>
+  <si>
+    <t>POS PURCHASE @2057UOKN-T078819 2057UOKN DCIR POS</t>
+  </si>
+  <si>
+    <t>POS PURCHASE @2057NGA9-OPAY KILIMANJARO OZUMBA</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-INTERBANK-S72692491-12-03-2026</t>
+  </si>
+  <si>
+    <t>3/13/2026</t>
+  </si>
+  <si>
+    <t>3/13/2026 11:47:23 AM</t>
+  </si>
+  <si>
+    <t>SMS ALERT CHARGES 12MAR 26</t>
+  </si>
+  <si>
+    <t>3/16/2026</t>
+  </si>
+  <si>
+    <t>3/16/2026 6:43:03 AM</t>
+  </si>
+  <si>
+    <t>POS PURCHASE @20574GQX-PAYCOM NIGERIA LIMITED PL</t>
+  </si>
+  <si>
+    <t>3/16/2026 7:06:24 AM</t>
+  </si>
+  <si>
+    <t>3/16/2026 12:04:17 PM</t>
+  </si>
+  <si>
+    <t>POS PURCHASE @2MP1J6GA-T321981 2MP1J6GA DCIR POS</t>
+  </si>
+  <si>
+    <t>3/16/2026 12:19:50 PM</t>
+  </si>
+  <si>
+    <t>POS TRANSFER @2ZN12TYC-FAIRMONEY MFB          IKEJ</t>
+  </si>
+  <si>
+    <t>3/16/2026 9:48:44 PM</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-INTERBANK-S82250599-16-03-2026</t>
+  </si>
+  <si>
+    <t>3/16/2026 9:54:25 PM</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-POS-S82786028-16-03-2026</t>
+  </si>
+  <si>
+    <t>3/16/2026 9:57:17 PM</t>
+  </si>
+  <si>
+    <t>STAMP DUTY CHARGE-POS-S82820153-16-03-2026</t>
+  </si>
+  <si>
+    <t>3/2/2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>3/2/2026 8:00:30 PM</t>
+  </si>
+  <si>
+    <t>400000</t>
+  </si>
+  <si>
+    <t>3/3/2026</t>
+  </si>
+  <si>
+    <t>3/3/2026 11:25:34 AM</t>
+  </si>
+  <si>
+    <t>3/3/2026 1:30:05 PM</t>
+  </si>
+  <si>
+    <t>3/3/2026 9:53:30 PM</t>
+  </si>
+  <si>
+    <t>3/3/2026 9:55:35 PM</t>
+  </si>
+  <si>
+    <t>3/5/2026</t>
+  </si>
+  <si>
+    <t>3/5/2026 11:43:19 AM</t>
+  </si>
+  <si>
+    <t>3/5/2026 2:54:10 PM</t>
+  </si>
+  <si>
+    <t>3/5/2026 9:28:43 PM</t>
+  </si>
+  <si>
+    <t>3/5/2026 9:29:29 PM</t>
+  </si>
+  <si>
+    <t>3/6/2026</t>
+  </si>
+  <si>
+    <t>3/6/2026 7:17:26 PM</t>
+  </si>
+  <si>
+    <t>3/9/2026</t>
+  </si>
+  <si>
+    <t>3/9/2026 10:31:54 AM</t>
+  </si>
+  <si>
+    <t>3/9/2026 10:47:05 AM</t>
+  </si>
+  <si>
+    <t>3/9/2026 8:12:00 PM</t>
+  </si>
+  <si>
+    <t>3/9/2026 8:38:36 PM</t>
+  </si>
+  <si>
+    <t>3/10/2026</t>
+  </si>
+  <si>
+    <t>3/10/2026 5:14:36 PM</t>
+  </si>
+  <si>
+    <t>3/10/2026 8:11:39 PM</t>
+  </si>
+  <si>
+    <t>3/11/2026</t>
+  </si>
+  <si>
+    <t>3/11/2026 4:13:21 AM</t>
+  </si>
+  <si>
+    <t>3/11/2026 7:31:26 AM</t>
+  </si>
+  <si>
+    <t>3/11/2026 1:40:45 PM</t>
+  </si>
+  <si>
+    <t>3/11/2026 4:52:34 PM</t>
+  </si>
+  <si>
+    <t>3/11/2026 9:00:28 PM</t>
+  </si>
+  <si>
+    <t>3/12/2026</t>
+  </si>
+  <si>
+    <t>3/12/2026 6:48:12 AM</t>
+  </si>
+  <si>
+    <t>3/12/2026 6:57:21 AM</t>
+  </si>
+  <si>
+    <t>3/12/2026 4:39:39 PM</t>
+  </si>
+  <si>
+    <t>3/12/2026 5:02:42 PM</t>
+  </si>
+  <si>
+    <t>3/12/2026 8:28:38 PM</t>
+  </si>
+  <si>
+    <t>charges</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -49,8 +363,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +645,1216 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H49"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="14.6328125" customWidth="1"/>
+    <col min="5" max="5" width="60.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2">
+        <v>84</v>
+      </c>
+      <c r="H2">
+        <v>539.69000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>527.69000000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4">
+        <v>12</v>
+      </c>
+      <c r="H4">
+        <v>515.69000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5">
+        <v>400515.69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6">
+        <v>30525</v>
+      </c>
+      <c r="H6">
+        <v>369990.69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7">
+        <v>103250</v>
+      </c>
+      <c r="H7">
+        <v>266740.69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>266640.69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>266590.69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10">
+        <v>50</v>
+      </c>
+      <c r="H10">
+        <v>266540.69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11">
+        <v>40000</v>
+      </c>
+      <c r="H11">
+        <v>226540.69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <v>226440.69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13">
+        <v>54000</v>
+      </c>
+      <c r="H13">
+        <v>172440.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <v>172340.69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>172290.69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16">
+        <v>50</v>
+      </c>
+      <c r="H16">
+        <v>172240.69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17">
+        <v>7661.25</v>
+      </c>
+      <c r="H17">
+        <v>164579.44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18">
+        <v>164479.44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19">
+        <v>4880</v>
+      </c>
+      <c r="H19">
+        <v>159599.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20">
+        <v>11490</v>
+      </c>
+      <c r="H20">
+        <v>148109.44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21">
+        <v>10000</v>
+      </c>
+      <c r="H21">
+        <v>138109.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22">
+        <v>50</v>
+      </c>
+      <c r="H22">
+        <v>138059.44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+      <c r="H23">
+        <v>138047.44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24">
+        <v>36</v>
+      </c>
+      <c r="H24">
+        <v>138011.44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25">
+        <v>48</v>
+      </c>
+      <c r="H25">
+        <v>137963.44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26">
+        <v>24</v>
+      </c>
+      <c r="H26">
+        <v>137939.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27">
+        <v>10000</v>
+      </c>
+      <c r="H27">
+        <v>127939.44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28">
+        <v>36</v>
+      </c>
+      <c r="H28">
+        <v>127903.44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29">
+        <v>50</v>
+      </c>
+      <c r="H29">
+        <v>127853.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30">
+        <v>12</v>
+      </c>
+      <c r="H30">
+        <v>127841.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31">
+        <v>55000</v>
+      </c>
+      <c r="H31">
+        <v>72841.440000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
+        <v>72741.440000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33">
+        <v>8400</v>
+      </c>
+      <c r="H33">
+        <v>64341.440000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34">
+        <v>5450</v>
+      </c>
+      <c r="H34">
+        <v>58891.44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35">
+        <v>50</v>
+      </c>
+      <c r="H35">
+        <v>58841.440000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36">
+        <v>48</v>
+      </c>
+      <c r="H36">
+        <v>58793.440000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G37">
+        <v>3000</v>
+      </c>
+      <c r="H37">
+        <v>55793.440000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38">
+        <v>17500</v>
+      </c>
+      <c r="H38">
+        <v>38293.440000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39">
+        <v>100</v>
+      </c>
+      <c r="H39">
+        <v>38193.440000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40">
+        <v>20000</v>
+      </c>
+      <c r="H40">
+        <v>18193.439999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41">
+        <v>16500</v>
+      </c>
+      <c r="H41">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" s="1">
+        <v>50</v>
+      </c>
+      <c r="H42">
+        <v>1643.44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43">
+        <v>50</v>
+      </c>
+      <c r="H43">
+        <v>1593.44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" t="s">
+        <v>57</v>
+      </c>
+      <c r="F44" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" s="1">
+        <v>50</v>
+      </c>
+      <c r="H44">
+        <v>1543.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" t="s">
+        <v>0</v>
+      </c>
+      <c r="E45" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" t="s">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" t="s">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>